--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancentralrd-my.sharepoint.com/personal/l_lopez_bancentral_gov_do/Documents/Alertas Telegram/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{35B649C4-0AB4-4C9F-A2C4-3E11E388F1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1C7CA42-AF9B-4982-8EE2-AB2C37D47F96}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E173D6A-FFC0-48CA-A3E3-02D3751184DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>https://www.bancentral.gov.do/a/d/2714-facilidades-permanentes-de-contraccion-y-expansion-monetaria-a-plazo-de-un-dia</t>
   </si>
   <si>
-    <t>Operaciones</t>
-  </si>
-  <si>
     <t>Fiscal</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-turismo/documents/lleg_total.xls?v=1786718170603</t>
+  </si>
+  <si>
+    <t>Expansion/Contraccion</t>
   </si>
 </sst>
 </file>
@@ -163,10 +163,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -489,15 +485,15 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -505,7 +501,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -513,36 +509,36 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -550,42 +546,42 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
